--- a/Excel/Item.xlsx
+++ b/Excel/Item.xlsx
@@ -26,8 +26,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={849FC151-4893-450E-8B24-4D0093861A86}</author>
-    <author>tc={1E423831-5847-4F84-A07F-CEFF5CD98D38}</author>
+    <author>tc={CD602728-33A3-4002-BBFC-6F1BB7A6A301}</author>
+    <author>tc={66998419-ED7C-48BD-8F52-149E19777794}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t/>
   </si>
@@ -1197,6 +1197,39 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>伏特加、莫斯科骡子</t>
+  </si>
+  <si>
+    <t>朗姆、自由古巴</t>
+  </si>
+  <si>
+    <t>威士忌、威士忌酸</t>
+  </si>
+  <si>
+    <t>金酒、金汤力、内格罗尼</t>
+  </si>
+  <si>
+    <t>伏特加、莫斯科骡子、大都会</t>
+  </si>
+  <si>
+    <t>朗姆、自由古巴、莫吉托</t>
+  </si>
+  <si>
+    <t>柑橘类果汁与果皮：青柠汁；橙味力娇酒亦带此标签。</t>
+  </si>
+  <si>
+    <t>汤力水、可乐</t>
+  </si>
+  <si>
+    <t>君度、金巴利</t>
+  </si>
+  <si>
+    <t>金酒、苦味、力娇酒</t>
+  </si>
+  <si>
+    <t>intelligence</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1306,7 @@
   <cellStyleXfs>
     <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1311,6 +1344,7 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1320,7 +1354,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <tc2018:personList xmlns:tc2018="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="tc2018">
-  <tc2018:person displayName="銀河騎士" id="{D42D0225-51A1-40B7-B427-2AC98B6EEA95}"/>
+  <tc2018:person displayName="銀河騎士" id="{F60A727E-0A88-4B99-9DF1-06B02B75AFB4}"/>
 </tc2018:personList>
 </file>
 
@@ -1587,7 +1621,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="">
-  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{D42D0225-51A1-40B7-B427-2AC98B6EEA95}" id="{849FC151-4893-450E-8B24-4D0093861A86}">
+  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{F60A727E-0A88-4B99-9DF1-06B02B75AFB4}" id="{CD602728-33A3-4002-BBFC-6F1BB7A6A301}">
     <text>0=货币
 1=武器
 2=防具
@@ -1595,7 +1629,7 @@
 4=材料
 5=消耗品</text>
   </threadedComment>
-  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{D42D0225-51A1-40B7-B427-2AC98B6EEA95}" id="{1E423831-5847-4F84-A07F-CEFF5CD98D38}">
+  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{F60A727E-0A88-4B99-9DF1-06B02B75AFB4}" id="{66998419-ED7C-48BD-8F52-149E19777794}">
     <text>1=普通
 2=稀有
 3=史诗
@@ -1607,16 +1641,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
-  <dimension ref="Z203"/>
+  <dimension ref="Z167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.7109" customWidth="1"/>
     <col min="2" max="2" width="3.0625" customWidth="1"/>
-    <col min="3" max="3" width="8.29297" customWidth="1"/>
+    <col min="3" max="3" width="11.043" customWidth="1"/>
     <col min="4" max="4" width="10.3008" customWidth="1"/>
     <col min="5" max="5" width="6.30078" customWidth="1"/>
     <col min="6" max="6" width="9.07031" customWidth="1"/>
-    <col min="7" max="7" width="20.2422" customWidth="1"/>
+    <col min="7" max="7" width="28.4531" customWidth="1"/>
     <col min="8" max="8" width="5.40234" customWidth="1"/>
     <col min="9" max="11" width="8.29297" customWidth="1"/>
     <col min="12" max="14" width="8.29297" customWidth="1"/>
@@ -1717,7 +1751,7 @@
         <v>28</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>29</v>
+        <v>390</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>30</v>
@@ -1779,7 +1813,7 @@
         <v>29</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>379</v>
+        <v>35</v>
       </c>
       <c r="P3" s="4" t="s"/>
       <c r="Q3" s="4" t="s"/>
@@ -2965,10 +2999,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E29" s="4">
         <v>1</v>
@@ -2976,11 +3010,9 @@
       <c r="F29" s="4">
         <v>4</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>121</v>
-      </c>
+      <c r="G29" s="8" t="s"/>
       <c r="H29" s="4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I29" s="4">
         <v>0</v>
@@ -3001,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="P29" s="4" t="s"/>
       <c r="Q29" s="4" t="s"/>
@@ -3013,10 +3045,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E30" s="4">
         <v>1</v>
@@ -3026,7 +3058,7 @@
       </c>
       <c r="G30" s="8" t="s"/>
       <c r="H30" s="4">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="I30" s="4">
         <v>0</v>
@@ -3047,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P30" s="4" t="s"/>
       <c r="Q30" s="4" t="s"/>
@@ -3059,20 +3091,20 @@
         <v>28</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E31" s="4">
         <v>1</v>
       </c>
       <c r="F31" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="8" t="s"/>
       <c r="H31" s="4">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I31" s="4">
         <v>0</v>
@@ -3087,13 +3119,13 @@
         <v>0</v>
       </c>
       <c r="M31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="P31" s="4" t="s"/>
       <c r="Q31" s="4" t="s"/>
@@ -3105,22 +3137,20 @@
         <v>29</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E32" s="4">
         <v>2</v>
       </c>
       <c r="F32" s="4">
-        <v>4</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>131</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G32" s="8" t="s"/>
       <c r="H32" s="4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I32" s="4">
         <v>0</v>
@@ -3135,13 +3165,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P32" s="4" t="s"/>
       <c r="Q32" s="4" t="s"/>
@@ -3153,20 +3183,20 @@
         <v>30</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E33" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="4">
         <v>5</v>
       </c>
       <c r="G33" s="8" t="s"/>
       <c r="H33" s="4">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I33" s="4">
         <v>0</v>
@@ -3184,10 +3214,10 @@
         <v>2</v>
       </c>
       <c r="N33" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="P33" s="4" t="s"/>
       <c r="Q33" s="4" t="s"/>
@@ -3199,20 +3229,20 @@
         <v>31</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E34" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4">
         <v>5</v>
       </c>
       <c r="G34" s="8" t="s"/>
       <c r="H34" s="4">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
@@ -3233,7 +3263,7 @@
         <v>3</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="P34" s="4" t="s"/>
       <c r="Q34" s="4" t="s"/>
@@ -3245,20 +3275,20 @@
         <v>32</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E35" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="4">
         <v>5</v>
       </c>
       <c r="G35" s="8" t="s"/>
       <c r="H35" s="4">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I35" s="4">
         <v>0</v>
@@ -3276,10 +3306,10 @@
         <v>2</v>
       </c>
       <c r="N35" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="P35" s="4" t="s"/>
       <c r="Q35" s="4" t="s"/>
@@ -3291,20 +3321,20 @@
         <v>33</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
       </c>
       <c r="F36" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="8" t="s"/>
       <c r="H36" s="4">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I36" s="4">
         <v>0</v>
@@ -3319,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="P36" s="4" t="s"/>
       <c r="Q36" s="4" t="s"/>
@@ -3337,20 +3367,20 @@
         <v>34</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E37" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="8" t="s"/>
       <c r="H37" s="4">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="I37" s="4">
         <v>0</v>
@@ -3365,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N37" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P37" s="4" t="s"/>
       <c r="Q37" s="4" t="s"/>
@@ -3383,10 +3413,10 @@
         <v>35</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -3396,7 +3426,7 @@
       </c>
       <c r="G38" s="8" t="s"/>
       <c r="H38" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I38" s="4">
         <v>0</v>
@@ -3417,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="P38" s="4" t="s"/>
       <c r="Q38" s="4" t="s"/>
@@ -3429,20 +3459,20 @@
         <v>36</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E39" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4">
         <v>4</v>
       </c>
       <c r="G39" s="8" t="s"/>
       <c r="H39" s="4">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="I39" s="4">
         <v>0</v>
@@ -3463,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="P39" s="4" t="s"/>
       <c r="Q39" s="4" t="s"/>
@@ -3475,20 +3505,20 @@
         <v>37</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E40" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="s"/>
       <c r="H40" s="4">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I40" s="4">
         <v>0</v>
@@ -3509,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="P40" s="4" t="s"/>
       <c r="Q40" s="4" t="s"/>
@@ -3521,20 +3551,20 @@
         <v>38</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E41" s="4">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4">
         <v>3</v>
-      </c>
-      <c r="F41" s="4">
-        <v>4</v>
       </c>
       <c r="G41" s="8" t="s"/>
       <c r="H41" s="4">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="I41" s="4">
         <v>0</v>
@@ -3555,125 +3585,121 @@
         <v>0</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P41" s="4" t="s"/>
       <c r="Q41" s="4" t="s"/>
       <c r="R41" s="4" t="s"/>
     </row>
-    <row r="42" spans="1:18" ht="24" customHeight="1">
-      <c r="A42" s="4" t="s"/>
+    <row r="42" spans="2:15" ht="24" customHeight="1">
       <c r="B42" s="4">
         <v>39</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E42" s="4">
-        <v>2</v>
-      </c>
-      <c r="F42" s="4">
-        <v>3</v>
-      </c>
-      <c r="G42" s="8" t="s"/>
-      <c r="H42" s="4">
-        <v>80</v>
-      </c>
-      <c r="I42" s="4">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4">
-        <v>0</v>
-      </c>
-      <c r="M42" s="4">
-        <v>0</v>
-      </c>
-      <c r="N42" s="4">
-        <v>0</v>
-      </c>
-      <c r="O42" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="P42" s="4" t="s"/>
-      <c r="Q42" s="4" t="s"/>
-      <c r="R42" s="4" t="s"/>
-    </row>
-    <row r="43" spans="1:18" ht="24" customHeight="1">
-      <c r="A43" s="4" t="s"/>
+      <c r="C42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>166</v>
+      </c>
+      <c r="H42">
+        <v>120</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" ht="24" customHeight="1">
       <c r="B43" s="4">
         <v>40</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" s="4">
+      <c r="C43" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>169</v>
+      </c>
+      <c r="H43">
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" ht="24" customHeight="1">
+      <c r="B44" s="4">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44">
         <v>2</v>
-      </c>
-      <c r="F43" s="4">
-        <v>3</v>
-      </c>
-      <c r="G43" s="8" t="s"/>
-      <c r="H43" s="4">
-        <v>60</v>
-      </c>
-      <c r="I43" s="4">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4">
-        <v>0</v>
-      </c>
-      <c r="K43" s="4">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4">
-        <v>0</v>
-      </c>
-      <c r="M43" s="4">
-        <v>0</v>
-      </c>
-      <c r="N43" s="4">
-        <v>0</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P43" s="4" t="s"/>
-      <c r="Q43" s="4" t="s"/>
-      <c r="R43" s="4" t="s"/>
-    </row>
-    <row r="44" spans="2:15" ht="24" customHeight="1">
-      <c r="B44">
-        <v>41</v>
-      </c>
-      <c r="C44" t="s">
-        <v>166</v>
-      </c>
-      <c r="D44" t="s">
-        <v>167</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
       </c>
       <c r="F44">
         <v>4</v>
       </c>
       <c r="G44" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H44">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3694,18 +3720,18 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="2:15" ht="24" customHeight="1">
-      <c r="B45">
+      <c r="B45" s="4">
         <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -3714,10 +3740,10 @@
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H45">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3738,30 +3764,30 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="2:15" ht="24" customHeight="1">
-      <c r="B46">
+      <c r="B46" s="4">
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="D46" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
         <v>4</v>
       </c>
       <c r="G46" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="H46">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3782,30 +3808,30 @@
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="2:15" ht="24" customHeight="1">
-      <c r="B47">
+      <c r="B47" s="4">
         <v>44</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D47" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47">
         <v>4</v>
       </c>
       <c r="G47" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="H47">
-        <v>160</v>
+        <v>7</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3826,30 +3852,30 @@
         <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="2:15" ht="24" customHeight="1">
-      <c r="B48">
+      <c r="B48" s="4">
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="D48" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
         <v>4</v>
       </c>
       <c r="G48" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="H48">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3870,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="2:15" ht="24" customHeight="1">
-      <c r="B49">
+      <c r="B49" s="4">
         <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -3890,10 +3916,10 @@
         <v>4</v>
       </c>
       <c r="G49" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="H49">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3914,30 +3940,30 @@
         <v>0</v>
       </c>
       <c r="O49" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="2:15" ht="24" customHeight="1">
-      <c r="B50">
+      <c r="B50" s="4">
         <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>4</v>
       </c>
       <c r="G50" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="H50">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3958,30 +3984,30 @@
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="2:15" ht="24" customHeight="1">
-      <c r="B51">
+      <c r="B51" s="4">
         <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>188</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>4</v>
       </c>
       <c r="G51" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="H51">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -4002,30 +4028,30 @@
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="2:15" ht="24" customHeight="1">
-      <c r="B52">
+      <c r="B52" s="4">
         <v>49</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52">
         <v>4</v>
       </c>
       <c r="G52" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="H52">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -4046,18 +4072,18 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="2:15" ht="24" customHeight="1">
-      <c r="B53">
+      <c r="B53" s="4">
         <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4066,10 +4092,10 @@
         <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4090,74 +4116,74 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="2:15" ht="24" customHeight="1">
-      <c r="B54">
+      <c r="B54" s="8">
         <v>51</v>
       </c>
-      <c r="C54" t="s">
-        <v>199</v>
-      </c>
-      <c r="D54" t="s">
-        <v>200</v>
-      </c>
-      <c r="E54">
+      <c r="C54" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="E54" s="15">
         <v>1</v>
       </c>
-      <c r="F54">
-        <v>4</v>
-      </c>
-      <c r="G54" t="s">
-        <v>131</v>
-      </c>
-      <c r="H54">
+      <c r="F54" s="15">
         <v>6</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54" t="s">
-        <v>201</v>
+      <c r="G54" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="H54" s="15">
+        <v>45</v>
+      </c>
+      <c r="I54" s="15">
+        <v>0</v>
+      </c>
+      <c r="J54" s="15">
+        <v>0</v>
+      </c>
+      <c r="K54" s="15">
+        <v>0</v>
+      </c>
+      <c r="L54" s="15">
+        <v>0</v>
+      </c>
+      <c r="M54" s="15">
+        <v>0</v>
+      </c>
+      <c r="N54" s="15">
+        <v>0</v>
+      </c>
+      <c r="O54" s="15" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="2:15" ht="24" customHeight="1">
-      <c r="B55">
+      <c r="B55" s="4">
         <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G55" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="H55">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4178,118 +4204,118 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="2:15" ht="24" customHeight="1">
-      <c r="B56">
+      <c r="B56" s="8">
         <v>53</v>
       </c>
-      <c r="C56" t="s">
-        <v>206</v>
-      </c>
-      <c r="D56" t="s">
-        <v>207</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56">
-        <v>4</v>
-      </c>
-      <c r="G56" t="s">
-        <v>208</v>
-      </c>
-      <c r="H56">
-        <v>5</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>209</v>
+      <c r="C56" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" s="15">
+        <v>2</v>
+      </c>
+      <c r="F56" s="15">
+        <v>6</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="H56" s="15">
+        <v>100</v>
+      </c>
+      <c r="I56" s="15">
+        <v>0</v>
+      </c>
+      <c r="J56" s="15">
+        <v>0</v>
+      </c>
+      <c r="K56" s="15">
+        <v>0</v>
+      </c>
+      <c r="L56" s="15">
+        <v>0</v>
+      </c>
+      <c r="M56" s="15">
+        <v>0</v>
+      </c>
+      <c r="N56" s="15">
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="2:15" ht="24" customHeight="1">
-      <c r="B57">
+      <c r="B57" s="8">
         <v>54</v>
       </c>
-      <c r="C57" t="s">
-        <v>210</v>
-      </c>
-      <c r="D57" t="s">
-        <v>211</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57">
-        <v>4</v>
-      </c>
-      <c r="G57" t="s">
-        <v>208</v>
-      </c>
-      <c r="H57">
-        <v>7</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57" t="s">
-        <v>212</v>
+      <c r="C57" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57" s="15">
+        <v>3</v>
+      </c>
+      <c r="F57" s="15">
+        <v>6</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="H57" s="15">
+        <v>150</v>
+      </c>
+      <c r="I57" s="15">
+        <v>0</v>
+      </c>
+      <c r="J57" s="15">
+        <v>0</v>
+      </c>
+      <c r="K57" s="15">
+        <v>0</v>
+      </c>
+      <c r="L57" s="15">
+        <v>0</v>
+      </c>
+      <c r="M57" s="15">
+        <v>0</v>
+      </c>
+      <c r="N57" s="15">
+        <v>0</v>
+      </c>
+      <c r="O57" s="15" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="58" spans="2:15" ht="24" customHeight="1">
-      <c r="B58">
+      <c r="B58" s="4">
         <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="D58" t="s">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4310,30 +4336,30 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="24" customHeight="1">
-      <c r="B59">
+      <c r="B59" s="4">
         <v>56</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="D59" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59" t="s">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="H59">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4354,1109 +4380,34 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" ht="24" customHeight="1">
-      <c r="B60">
-        <v>57</v>
-      </c>
-      <c r="C60" t="s">
-        <v>220</v>
-      </c>
-      <c r="D60" t="s">
-        <v>221</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60">
-        <v>4</v>
-      </c>
-      <c r="G60" t="s">
-        <v>121</v>
-      </c>
-      <c r="H60">
-        <v>10</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" ht="24" customHeight="1">
-      <c r="B61">
-        <v>58</v>
-      </c>
-      <c r="C61" t="s">
-        <v>223</v>
-      </c>
-      <c r="D61" t="s">
-        <v>224</v>
-      </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>4</v>
-      </c>
-      <c r="G61" t="s">
-        <v>121</v>
-      </c>
-      <c r="H61">
-        <v>12</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" ht="24" customHeight="1">
-      <c r="B62">
-        <v>59</v>
-      </c>
-      <c r="C62" t="s">
-        <v>226</v>
-      </c>
-      <c r="D62" t="s">
-        <v>227</v>
-      </c>
-      <c r="E62">
-        <v>2</v>
-      </c>
-      <c r="F62">
-        <v>4</v>
-      </c>
-      <c r="G62" t="s">
-        <v>228</v>
-      </c>
-      <c r="H62">
-        <v>25</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" ht="24" customHeight="1">
-      <c r="B63">
-        <v>60</v>
-      </c>
-      <c r="C63" t="s">
-        <v>230</v>
-      </c>
-      <c r="D63" t="s">
-        <v>231</v>
-      </c>
-      <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="F63">
-        <v>4</v>
-      </c>
-      <c r="G63" t="s">
-        <v>232</v>
-      </c>
-      <c r="H63">
-        <v>45</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" ht="24" customHeight="1">
-      <c r="B64">
-        <v>61</v>
-      </c>
-      <c r="C64" t="s">
-        <v>234</v>
-      </c>
-      <c r="D64" t="s">
-        <v>235</v>
-      </c>
-      <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="F64">
-        <v>4</v>
-      </c>
-      <c r="G64" t="s">
-        <v>236</v>
-      </c>
-      <c r="H64">
-        <v>40</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" ht="24" customHeight="1">
-      <c r="B65">
-        <v>62</v>
-      </c>
-      <c r="C65" t="s">
-        <v>238</v>
-      </c>
-      <c r="D65" t="s">
-        <v>239</v>
-      </c>
-      <c r="E65">
-        <v>2</v>
-      </c>
-      <c r="F65">
-        <v>4</v>
-      </c>
-      <c r="G65" t="s">
-        <v>240</v>
-      </c>
-      <c r="H65">
-        <v>45</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" ht="24" customHeight="1">
-      <c r="B66">
-        <v>63</v>
-      </c>
-      <c r="C66" t="s">
-        <v>242</v>
-      </c>
-      <c r="D66" t="s">
-        <v>243</v>
-      </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
-      <c r="F66">
-        <v>4</v>
-      </c>
-      <c r="G66" t="s">
-        <v>244</v>
-      </c>
-      <c r="H66">
-        <v>38</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" ht="24" customHeight="1">
-      <c r="B67">
-        <v>64</v>
-      </c>
-      <c r="C67" t="s">
-        <v>246</v>
-      </c>
-      <c r="D67" t="s">
-        <v>247</v>
-      </c>
-      <c r="E67">
-        <v>2</v>
-      </c>
-      <c r="F67">
-        <v>4</v>
-      </c>
-      <c r="G67" t="s">
-        <v>244</v>
-      </c>
-      <c r="H67">
-        <v>38</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" ht="24" customHeight="1">
-      <c r="B68">
-        <v>65</v>
-      </c>
-      <c r="C68" t="s">
-        <v>249</v>
-      </c>
-      <c r="D68" t="s">
-        <v>250</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>4</v>
-      </c>
-      <c r="G68" t="s">
-        <v>251</v>
-      </c>
-      <c r="H68">
-        <v>2</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="69" spans="2:15" ht="24" customHeight="1">
-      <c r="B69">
-        <v>66</v>
-      </c>
-      <c r="C69" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" t="s">
-        <v>254</v>
-      </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
-      <c r="F69">
-        <v>6</v>
-      </c>
-      <c r="G69" t="s">
-        <v>255</v>
-      </c>
-      <c r="H69">
-        <v>90</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="70" spans="2:15" ht="24" customHeight="1">
-      <c r="B70">
-        <v>67</v>
-      </c>
-      <c r="C70" t="s">
-        <v>257</v>
-      </c>
-      <c r="D70" t="s">
-        <v>258</v>
-      </c>
-      <c r="E70">
-        <v>3</v>
-      </c>
-      <c r="F70">
-        <v>6</v>
-      </c>
-      <c r="G70" t="s">
-        <v>259</v>
-      </c>
-      <c r="H70">
-        <v>100</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="71" spans="2:15" ht="24" customHeight="1">
-      <c r="B71">
-        <v>68</v>
-      </c>
-      <c r="C71" t="s">
-        <v>261</v>
-      </c>
-      <c r="D71" t="s">
-        <v>262</v>
-      </c>
-      <c r="E71">
-        <v>3</v>
-      </c>
-      <c r="F71">
-        <v>6</v>
-      </c>
-      <c r="G71" t="s">
-        <v>263</v>
-      </c>
-      <c r="H71">
-        <v>140</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="72" spans="2:15" ht="24" customHeight="1">
-      <c r="B72">
-        <v>69</v>
-      </c>
-      <c r="C72" t="s">
-        <v>265</v>
-      </c>
-      <c r="D72" t="s">
-        <v>266</v>
-      </c>
-      <c r="E72">
-        <v>2</v>
-      </c>
-      <c r="F72">
-        <v>6</v>
-      </c>
-      <c r="G72" t="s">
-        <v>267</v>
-      </c>
-      <c r="H72">
-        <v>100</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" ht="24" customHeight="1">
-      <c r="B73">
-        <v>70</v>
-      </c>
-      <c r="C73" t="s">
-        <v>269</v>
-      </c>
-      <c r="D73" t="s">
-        <v>270</v>
-      </c>
-      <c r="E73">
-        <v>2</v>
-      </c>
-      <c r="F73">
-        <v>6</v>
-      </c>
-      <c r="G73" t="s">
-        <v>271</v>
-      </c>
-      <c r="H73">
-        <v>105</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="74" spans="2:15" ht="24" customHeight="1">
-      <c r="B74">
-        <v>71</v>
-      </c>
-      <c r="C74" t="s">
-        <v>273</v>
-      </c>
-      <c r="D74" t="s">
-        <v>274</v>
-      </c>
-      <c r="E74">
-        <v>3</v>
-      </c>
-      <c r="F74">
-        <v>6</v>
-      </c>
-      <c r="G74" t="s">
-        <v>275</v>
-      </c>
-      <c r="H74">
-        <v>150</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" ht="24" customHeight="1">
-      <c r="B75">
-        <v>72</v>
-      </c>
-      <c r="C75" t="s">
-        <v>277</v>
-      </c>
-      <c r="D75" t="s">
-        <v>278</v>
-      </c>
-      <c r="E75">
-        <v>2</v>
-      </c>
-      <c r="F75">
-        <v>6</v>
-      </c>
-      <c r="G75" t="s">
-        <v>279</v>
-      </c>
-      <c r="H75">
-        <v>85</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" ht="24" customHeight="1">
-      <c r="B76">
-        <v>73</v>
-      </c>
-      <c r="C76" t="s">
-        <v>281</v>
-      </c>
-      <c r="D76" t="s">
-        <v>282</v>
-      </c>
-      <c r="E76">
-        <v>2</v>
-      </c>
-      <c r="F76">
-        <v>6</v>
-      </c>
-      <c r="G76" t="s">
-        <v>283</v>
-      </c>
-      <c r="H76">
-        <v>80</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" ht="24" customHeight="1">
-      <c r="B77">
-        <v>74</v>
-      </c>
-      <c r="C77" t="s">
-        <v>285</v>
-      </c>
-      <c r="D77" t="s">
-        <v>286</v>
-      </c>
-      <c r="E77">
-        <v>2</v>
-      </c>
-      <c r="F77">
-        <v>6</v>
-      </c>
-      <c r="G77" t="s">
-        <v>287</v>
-      </c>
-      <c r="H77">
-        <v>75</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="78" spans="2:15" ht="24" customHeight="1">
-      <c r="B78">
-        <v>75</v>
-      </c>
-      <c r="C78" t="s">
-        <v>289</v>
-      </c>
-      <c r="D78" t="s">
-        <v>290</v>
-      </c>
-      <c r="E78">
-        <v>3</v>
-      </c>
-      <c r="F78">
-        <v>6</v>
-      </c>
-      <c r="G78" t="s">
-        <v>291</v>
-      </c>
-      <c r="H78">
-        <v>120</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="79" spans="2:15" ht="24" customHeight="1">
-      <c r="B79">
-        <v>76</v>
-      </c>
-      <c r="C79" t="s">
-        <v>293</v>
-      </c>
-      <c r="D79" t="s">
-        <v>294</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
-      </c>
-      <c r="F79">
-        <v>6</v>
-      </c>
-      <c r="G79" t="s">
-        <v>295</v>
-      </c>
-      <c r="H79">
-        <v>125</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="80" spans="2:15" ht="24" customHeight="1">
-      <c r="B80">
-        <v>77</v>
-      </c>
-      <c r="C80" t="s">
-        <v>297</v>
-      </c>
-      <c r="D80" t="s">
-        <v>298</v>
-      </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
-      <c r="F80">
-        <v>6</v>
-      </c>
-      <c r="G80" t="s">
-        <v>299</v>
-      </c>
-      <c r="H80">
-        <v>110</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="81" spans="2:15" ht="24" customHeight="1">
-      <c r="B81">
-        <v>78</v>
-      </c>
-      <c r="C81" t="s">
-        <v>301</v>
-      </c>
-      <c r="D81" t="s">
-        <v>302</v>
-      </c>
-      <c r="E81">
-        <v>3</v>
-      </c>
-      <c r="F81">
-        <v>6</v>
-      </c>
-      <c r="G81" t="s">
-        <v>303</v>
-      </c>
-      <c r="H81">
-        <v>130</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81">
-        <v>0</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="82" spans="2:15" ht="24" customHeight="1">
-      <c r="B82">
-        <v>79</v>
-      </c>
-      <c r="C82" t="s">
-        <v>305</v>
-      </c>
-      <c r="D82" t="s">
-        <v>306</v>
-      </c>
-      <c r="E82">
-        <v>3</v>
-      </c>
-      <c r="F82">
-        <v>6</v>
-      </c>
-      <c r="G82" t="s">
-        <v>307</v>
-      </c>
-      <c r="H82">
-        <v>145</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>0</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="83" spans="2:15" ht="24" customHeight="1">
-      <c r="B83">
-        <v>80</v>
-      </c>
-      <c r="C83" t="s">
-        <v>309</v>
-      </c>
-      <c r="D83" t="s">
-        <v>310</v>
-      </c>
-      <c r="E83">
-        <v>3</v>
-      </c>
-      <c r="F83">
-        <v>6</v>
-      </c>
-      <c r="G83" t="s">
-        <v>311</v>
-      </c>
-      <c r="H83">
-        <v>155</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
-      <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="2:15" ht="24" customHeight="1">
-      <c r="B84">
-        <v>81</v>
-      </c>
-      <c r="C84" t="s">
-        <v>313</v>
-      </c>
-      <c r="D84" t="s">
-        <v>314</v>
-      </c>
-      <c r="E84">
-        <v>2</v>
-      </c>
-      <c r="F84">
-        <v>6</v>
-      </c>
-      <c r="G84" t="s">
-        <v>315</v>
-      </c>
-      <c r="H84">
-        <v>95</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84">
-        <v>0</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84" t="s">
-        <v>316</v>
-      </c>
-    </row>
+    <row r="60" spans="1:30" ht="24" customHeight="1"/>
+    <row r="61" spans="1:30" ht="24" customHeight="1"/>
+    <row r="62" spans="1:30" ht="24" customHeight="1"/>
+    <row r="63" spans="1:30" ht="24" customHeight="1"/>
+    <row r="64" spans="1:30" ht="24" customHeight="1"/>
+    <row r="65" spans="1:30" ht="24" customHeight="1"/>
+    <row r="66" spans="1:30" ht="24" customHeight="1"/>
+    <row r="67" spans="1:30" ht="24" customHeight="1"/>
+    <row r="68" spans="1:30" ht="24" customHeight="1"/>
+    <row r="69" spans="1:30" ht="24" customHeight="1"/>
+    <row r="70" spans="1:30" ht="24" customHeight="1"/>
+    <row r="71" spans="1:30" ht="24" customHeight="1"/>
+    <row r="72" spans="1:30" ht="24" customHeight="1"/>
+    <row r="73" spans="1:30" ht="24" customHeight="1"/>
+    <row r="74" spans="1:30" ht="24" customHeight="1"/>
+    <row r="75" spans="1:30" ht="24" customHeight="1"/>
+    <row r="76" spans="1:30" ht="24" customHeight="1"/>
+    <row r="77" spans="1:30" ht="24" customHeight="1"/>
+    <row r="78" spans="1:30" ht="24" customHeight="1"/>
+    <row r="79" spans="1:30" ht="24" customHeight="1"/>
+    <row r="80" spans="1:30" ht="24" customHeight="1"/>
+    <row r="81" spans="1:30" ht="24" customHeight="1"/>
+    <row r="82" spans="1:30" ht="24" customHeight="1"/>
+    <row r="83" spans="1:30" ht="24" customHeight="1"/>
+    <row r="84" spans="1:30" ht="24" customHeight="1"/>
     <row r="85" spans="1:30" ht="24" customHeight="1"/>
     <row r="86" spans="1:30" ht="24" customHeight="1"/>
     <row r="87" spans="1:30" ht="24" customHeight="1"/>
@@ -5540,523 +4491,331 @@
     <row r="165" spans="1:30" ht="24" customHeight="1"/>
     <row r="166" spans="1:30" ht="24" customHeight="1"/>
     <row r="167" spans="1:30" ht="24" customHeight="1"/>
-    <row r="168" spans="1:30" ht="24" customHeight="1"/>
-    <row r="169" spans="1:30" ht="24" customHeight="1"/>
-    <row r="170" spans="1:30" ht="24" customHeight="1"/>
-    <row r="171" spans="1:30" ht="24" customHeight="1"/>
-    <row r="172" spans="1:30" ht="24" customHeight="1"/>
-    <row r="173" spans="1:30" ht="24" customHeight="1"/>
-    <row r="174" spans="1:30" ht="24" customHeight="1"/>
-    <row r="175" spans="1:30" ht="24" customHeight="1"/>
-    <row r="176" spans="1:30" ht="24" customHeight="1"/>
-    <row r="177" spans="1:30" ht="24" customHeight="1"/>
-    <row r="178" spans="1:30" ht="24" customHeight="1"/>
-    <row r="179" spans="1:30" ht="24" customHeight="1"/>
-    <row r="180" spans="1:30" ht="24" customHeight="1"/>
-    <row r="181" spans="1:30" ht="24" customHeight="1"/>
-    <row r="182" spans="1:30" ht="24" customHeight="1"/>
-    <row r="183" spans="1:30" ht="24" customHeight="1"/>
-    <row r="184" spans="1:30" ht="24" customHeight="1"/>
-    <row r="185" spans="1:30" ht="24" customHeight="1"/>
-    <row r="186" spans="1:30" ht="24" customHeight="1"/>
-    <row r="187" spans="1:30" ht="24" customHeight="1"/>
-    <row r="188" spans="1:30" ht="24" customHeight="1"/>
-    <row r="189" spans="1:30" ht="24" customHeight="1"/>
-    <row r="190" spans="1:30" ht="24" customHeight="1"/>
-    <row r="191" spans="1:30" ht="24" customHeight="1"/>
-    <row r="192" spans="1:30" ht="24" customHeight="1"/>
-    <row r="193" spans="1:30" ht="24" customHeight="1"/>
-    <row r="194" spans="1:30" ht="24" customHeight="1"/>
-    <row r="195" spans="1:30" ht="24" customHeight="1"/>
-    <row r="196" spans="1:30" ht="24" customHeight="1"/>
-    <row r="197" spans="1:30" ht="24" customHeight="1"/>
-    <row r="198" spans="1:30" ht="24" customHeight="1"/>
-    <row r="199" spans="1:30" ht="24" customHeight="1"/>
-    <row r="200" spans="1:30" ht="24" customHeight="1"/>
-    <row r="201" spans="1:30" ht="24" customHeight="1"/>
-    <row r="202" spans="1:30" ht="24" customHeight="1"/>
-    <row r="203" spans="1:30" ht="24" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B44">
-      <formula1>AND(B44&lt;&gt;"",COUNTIF($B$4:$B$204,B44)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B45">
-      <formula1>AND(B45&lt;&gt;"",COUNTIF($B$4:$B$204,B45)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B46">
-      <formula1>AND(B46&lt;&gt;"",COUNTIF($B$4:$B$204,B46)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B47">
-      <formula1>AND(B47&lt;&gt;"",COUNTIF($B$4:$B$204,B47)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B48">
-      <formula1>AND(B48&lt;&gt;"",COUNTIF($B$4:$B$204,B48)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B49">
-      <formula1>AND(B49&lt;&gt;"",COUNTIF($B$4:$B$204,B49)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B50">
-      <formula1>AND(B50&lt;&gt;"",COUNTIF($B$4:$B$204,B50)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B51">
-      <formula1>AND(B51&lt;&gt;"",COUNTIF($B$4:$B$204,B51)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B52">
-      <formula1>AND(B52&lt;&gt;"",COUNTIF($B$4:$B$204,B52)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B53">
-      <formula1>AND(B53&lt;&gt;"",COUNTIF($B$4:$B$204,B53)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B54">
-      <formula1>AND(B54&lt;&gt;"",COUNTIF($B$4:$B$204,B54)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B55">
-      <formula1>AND(B55&lt;&gt;"",COUNTIF($B$4:$B$204,B55)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B56">
-      <formula1>AND(B56&lt;&gt;"",COUNTIF($B$4:$B$204,B56)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B57">
-      <formula1>AND(B57&lt;&gt;"",COUNTIF($B$4:$B$204,B57)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B58">
-      <formula1>AND(B58&lt;&gt;"",COUNTIF($B$4:$B$204,B58)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B59">
-      <formula1>AND(B59&lt;&gt;"",COUNTIF($B$4:$B$204,B59)=1)</formula1>
-    </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B60">
-      <formula1>AND(B60&lt;&gt;"",COUNTIF($B$4:$B$204,B60)=1)</formula1>
+      <formula1>AND(B60&lt;&gt;"",COUNTIF($B$4:$B$168,B60)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B61">
-      <formula1>AND(B61&lt;&gt;"",COUNTIF($B$4:$B$204,B61)=1)</formula1>
+      <formula1>AND(B61&lt;&gt;"",COUNTIF($B$4:$B$168,B61)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B62">
-      <formula1>AND(B62&lt;&gt;"",COUNTIF($B$4:$B$204,B62)=1)</formula1>
+      <formula1>AND(B62&lt;&gt;"",COUNTIF($B$4:$B$168,B62)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B63">
-      <formula1>AND(B63&lt;&gt;"",COUNTIF($B$4:$B$204,B63)=1)</formula1>
+      <formula1>AND(B63&lt;&gt;"",COUNTIF($B$4:$B$168,B63)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B64">
-      <formula1>AND(B64&lt;&gt;"",COUNTIF($B$4:$B$204,B64)=1)</formula1>
+      <formula1>AND(B64&lt;&gt;"",COUNTIF($B$4:$B$168,B64)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B65">
-      <formula1>AND(B65&lt;&gt;"",COUNTIF($B$4:$B$204,B65)=1)</formula1>
+      <formula1>AND(B65&lt;&gt;"",COUNTIF($B$4:$B$168,B65)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B66">
-      <formula1>AND(B66&lt;&gt;"",COUNTIF($B$4:$B$204,B66)=1)</formula1>
+      <formula1>AND(B66&lt;&gt;"",COUNTIF($B$4:$B$168,B66)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B67">
-      <formula1>AND(B67&lt;&gt;"",COUNTIF($B$4:$B$204,B67)=1)</formula1>
+      <formula1>AND(B67&lt;&gt;"",COUNTIF($B$4:$B$168,B67)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B68">
-      <formula1>AND(B68&lt;&gt;"",COUNTIF($B$4:$B$204,B68)=1)</formula1>
+      <formula1>AND(B68&lt;&gt;"",COUNTIF($B$4:$B$168,B68)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B69">
-      <formula1>AND(B69&lt;&gt;"",COUNTIF($B$4:$B$204,B69)=1)</formula1>
+      <formula1>AND(B69&lt;&gt;"",COUNTIF($B$4:$B$168,B69)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B70">
-      <formula1>AND(B70&lt;&gt;"",COUNTIF($B$4:$B$204,B70)=1)</formula1>
+      <formula1>AND(B70&lt;&gt;"",COUNTIF($B$4:$B$168,B70)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B71">
-      <formula1>AND(B71&lt;&gt;"",COUNTIF($B$4:$B$204,B71)=1)</formula1>
+      <formula1>AND(B71&lt;&gt;"",COUNTIF($B$4:$B$168,B71)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B72">
-      <formula1>AND(B72&lt;&gt;"",COUNTIF($B$4:$B$204,B72)=1)</formula1>
+      <formula1>AND(B72&lt;&gt;"",COUNTIF($B$4:$B$168,B72)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B73">
-      <formula1>AND(B73&lt;&gt;"",COUNTIF($B$4:$B$204,B73)=1)</formula1>
+      <formula1>AND(B73&lt;&gt;"",COUNTIF($B$4:$B$168,B73)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B74">
-      <formula1>AND(B74&lt;&gt;"",COUNTIF($B$4:$B$204,B74)=1)</formula1>
+      <formula1>AND(B74&lt;&gt;"",COUNTIF($B$4:$B$168,B74)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B75">
-      <formula1>AND(B75&lt;&gt;"",COUNTIF($B$4:$B$204,B75)=1)</formula1>
+      <formula1>AND(B75&lt;&gt;"",COUNTIF($B$4:$B$168,B75)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B76">
-      <formula1>AND(B76&lt;&gt;"",COUNTIF($B$4:$B$204,B76)=1)</formula1>
+      <formula1>AND(B76&lt;&gt;"",COUNTIF($B$4:$B$168,B76)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B77">
-      <formula1>AND(B77&lt;&gt;"",COUNTIF($B$4:$B$204,B77)=1)</formula1>
+      <formula1>AND(B77&lt;&gt;"",COUNTIF($B$4:$B$168,B77)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B78">
-      <formula1>AND(B78&lt;&gt;"",COUNTIF($B$4:$B$204,B78)=1)</formula1>
+      <formula1>AND(B78&lt;&gt;"",COUNTIF($B$4:$B$168,B78)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B79">
-      <formula1>AND(B79&lt;&gt;"",COUNTIF($B$4:$B$204,B79)=1)</formula1>
+      <formula1>AND(B79&lt;&gt;"",COUNTIF($B$4:$B$168,B79)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B80">
-      <formula1>AND(B80&lt;&gt;"",COUNTIF($B$4:$B$204,B80)=1)</formula1>
+      <formula1>AND(B80&lt;&gt;"",COUNTIF($B$4:$B$168,B80)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B81">
-      <formula1>AND(B81&lt;&gt;"",COUNTIF($B$4:$B$204,B81)=1)</formula1>
+      <formula1>AND(B81&lt;&gt;"",COUNTIF($B$4:$B$168,B81)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B82">
-      <formula1>AND(B82&lt;&gt;"",COUNTIF($B$4:$B$204,B82)=1)</formula1>
+      <formula1>AND(B82&lt;&gt;"",COUNTIF($B$4:$B$168,B82)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B83">
-      <formula1>AND(B83&lt;&gt;"",COUNTIF($B$4:$B$204,B83)=1)</formula1>
+      <formula1>AND(B83&lt;&gt;"",COUNTIF($B$4:$B$168,B83)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B84">
-      <formula1>AND(B84&lt;&gt;"",COUNTIF($B$4:$B$204,B84)=1)</formula1>
+      <formula1>AND(B84&lt;&gt;"",COUNTIF($B$4:$B$168,B84)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B85">
-      <formula1>AND(B85&lt;&gt;"",COUNTIF($B$4:$B$204,B85)=1)</formula1>
+      <formula1>AND(B85&lt;&gt;"",COUNTIF($B$4:$B$168,B85)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B86">
-      <formula1>AND(B86&lt;&gt;"",COUNTIF($B$4:$B$204,B86)=1)</formula1>
+      <formula1>AND(B86&lt;&gt;"",COUNTIF($B$4:$B$168,B86)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B87">
-      <formula1>AND(B87&lt;&gt;"",COUNTIF($B$4:$B$204,B87)=1)</formula1>
+      <formula1>AND(B87&lt;&gt;"",COUNTIF($B$4:$B$168,B87)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B88">
-      <formula1>AND(B88&lt;&gt;"",COUNTIF($B$4:$B$204,B88)=1)</formula1>
+      <formula1>AND(B88&lt;&gt;"",COUNTIF($B$4:$B$168,B88)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B89">
-      <formula1>AND(B89&lt;&gt;"",COUNTIF($B$4:$B$204,B89)=1)</formula1>
+      <formula1>AND(B89&lt;&gt;"",COUNTIF($B$4:$B$168,B89)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B90">
-      <formula1>AND(B90&lt;&gt;"",COUNTIF($B$4:$B$204,B90)=1)</formula1>
+      <formula1>AND(B90&lt;&gt;"",COUNTIF($B$4:$B$168,B90)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B91">
-      <formula1>AND(B91&lt;&gt;"",COUNTIF($B$4:$B$204,B91)=1)</formula1>
+      <formula1>AND(B91&lt;&gt;"",COUNTIF($B$4:$B$168,B91)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B92">
-      <formula1>AND(B92&lt;&gt;"",COUNTIF($B$4:$B$204,B92)=1)</formula1>
+      <formula1>AND(B92&lt;&gt;"",COUNTIF($B$4:$B$168,B92)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B93">
-      <formula1>AND(B93&lt;&gt;"",COUNTIF($B$4:$B$204,B93)=1)</formula1>
+      <formula1>AND(B93&lt;&gt;"",COUNTIF($B$4:$B$168,B93)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B94">
-      <formula1>AND(B94&lt;&gt;"",COUNTIF($B$4:$B$204,B94)=1)</formula1>
+      <formula1>AND(B94&lt;&gt;"",COUNTIF($B$4:$B$168,B94)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B95">
-      <formula1>AND(B95&lt;&gt;"",COUNTIF($B$4:$B$204,B95)=1)</formula1>
+      <formula1>AND(B95&lt;&gt;"",COUNTIF($B$4:$B$168,B95)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B96">
-      <formula1>AND(B96&lt;&gt;"",COUNTIF($B$4:$B$204,B96)=1)</formula1>
+      <formula1>AND(B96&lt;&gt;"",COUNTIF($B$4:$B$168,B96)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B97">
-      <formula1>AND(B97&lt;&gt;"",COUNTIF($B$4:$B$204,B97)=1)</formula1>
+      <formula1>AND(B97&lt;&gt;"",COUNTIF($B$4:$B$168,B97)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B98">
-      <formula1>AND(B98&lt;&gt;"",COUNTIF($B$4:$B$204,B98)=1)</formula1>
+      <formula1>AND(B98&lt;&gt;"",COUNTIF($B$4:$B$168,B98)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B99">
-      <formula1>AND(B99&lt;&gt;"",COUNTIF($B$4:$B$204,B99)=1)</formula1>
+      <formula1>AND(B99&lt;&gt;"",COUNTIF($B$4:$B$168,B99)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B100">
-      <formula1>AND(B100&lt;&gt;"",COUNTIF($B$4:$B$204,B100)=1)</formula1>
+      <formula1>AND(B100&lt;&gt;"",COUNTIF($B$4:$B$168,B100)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B101">
-      <formula1>AND(B101&lt;&gt;"",COUNTIF($B$4:$B$204,B101)=1)</formula1>
+      <formula1>AND(B101&lt;&gt;"",COUNTIF($B$4:$B$168,B101)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B102">
-      <formula1>AND(B102&lt;&gt;"",COUNTIF($B$4:$B$204,B102)=1)</formula1>
+      <formula1>AND(B102&lt;&gt;"",COUNTIF($B$4:$B$168,B102)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B103">
-      <formula1>AND(B103&lt;&gt;"",COUNTIF($B$4:$B$204,B103)=1)</formula1>
+      <formula1>AND(B103&lt;&gt;"",COUNTIF($B$4:$B$168,B103)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B104">
-      <formula1>AND(B104&lt;&gt;"",COUNTIF($B$4:$B$204,B104)=1)</formula1>
+      <formula1>AND(B104&lt;&gt;"",COUNTIF($B$4:$B$168,B104)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B105">
-      <formula1>AND(B105&lt;&gt;"",COUNTIF($B$4:$B$204,B105)=1)</formula1>
+      <formula1>AND(B105&lt;&gt;"",COUNTIF($B$4:$B$168,B105)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B106">
-      <formula1>AND(B106&lt;&gt;"",COUNTIF($B$4:$B$204,B106)=1)</formula1>
+      <formula1>AND(B106&lt;&gt;"",COUNTIF($B$4:$B$168,B106)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B107">
-      <formula1>AND(B107&lt;&gt;"",COUNTIF($B$4:$B$204,B107)=1)</formula1>
+      <formula1>AND(B107&lt;&gt;"",COUNTIF($B$4:$B$168,B107)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B108">
-      <formula1>AND(B108&lt;&gt;"",COUNTIF($B$4:$B$204,B108)=1)</formula1>
+      <formula1>AND(B108&lt;&gt;"",COUNTIF($B$4:$B$168,B108)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B109">
-      <formula1>AND(B109&lt;&gt;"",COUNTIF($B$4:$B$204,B109)=1)</formula1>
+      <formula1>AND(B109&lt;&gt;"",COUNTIF($B$4:$B$168,B109)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B110">
-      <formula1>AND(B110&lt;&gt;"",COUNTIF($B$4:$B$204,B110)=1)</formula1>
+      <formula1>AND(B110&lt;&gt;"",COUNTIF($B$4:$B$168,B110)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B111">
-      <formula1>AND(B111&lt;&gt;"",COUNTIF($B$4:$B$204,B111)=1)</formula1>
+      <formula1>AND(B111&lt;&gt;"",COUNTIF($B$4:$B$168,B111)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B112">
-      <formula1>AND(B112&lt;&gt;"",COUNTIF($B$4:$B$204,B112)=1)</formula1>
+      <formula1>AND(B112&lt;&gt;"",COUNTIF($B$4:$B$168,B112)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B113">
-      <formula1>AND(B113&lt;&gt;"",COUNTIF($B$4:$B$204,B113)=1)</formula1>
+      <formula1>AND(B113&lt;&gt;"",COUNTIF($B$4:$B$168,B113)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B114">
-      <formula1>AND(B114&lt;&gt;"",COUNTIF($B$4:$B$204,B114)=1)</formula1>
+      <formula1>AND(B114&lt;&gt;"",COUNTIF($B$4:$B$168,B114)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B115">
-      <formula1>AND(B115&lt;&gt;"",COUNTIF($B$4:$B$204,B115)=1)</formula1>
+      <formula1>AND(B115&lt;&gt;"",COUNTIF($B$4:$B$168,B115)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B116">
-      <formula1>AND(B116&lt;&gt;"",COUNTIF($B$4:$B$204,B116)=1)</formula1>
+      <formula1>AND(B116&lt;&gt;"",COUNTIF($B$4:$B$168,B116)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B117">
-      <formula1>AND(B117&lt;&gt;"",COUNTIF($B$4:$B$204,B117)=1)</formula1>
+      <formula1>AND(B117&lt;&gt;"",COUNTIF($B$4:$B$168,B117)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B118">
-      <formula1>AND(B118&lt;&gt;"",COUNTIF($B$4:$B$204,B118)=1)</formula1>
+      <formula1>AND(B118&lt;&gt;"",COUNTIF($B$4:$B$168,B118)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B119">
-      <formula1>AND(B119&lt;&gt;"",COUNTIF($B$4:$B$204,B119)=1)</formula1>
+      <formula1>AND(B119&lt;&gt;"",COUNTIF($B$4:$B$168,B119)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B120">
-      <formula1>AND(B120&lt;&gt;"",COUNTIF($B$4:$B$204,B120)=1)</formula1>
+      <formula1>AND(B120&lt;&gt;"",COUNTIF($B$4:$B$168,B120)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B121">
-      <formula1>AND(B121&lt;&gt;"",COUNTIF($B$4:$B$204,B121)=1)</formula1>
+      <formula1>AND(B121&lt;&gt;"",COUNTIF($B$4:$B$168,B121)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B122">
-      <formula1>AND(B122&lt;&gt;"",COUNTIF($B$4:$B$204,B122)=1)</formula1>
+      <formula1>AND(B122&lt;&gt;"",COUNTIF($B$4:$B$168,B122)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B123">
-      <formula1>AND(B123&lt;&gt;"",COUNTIF($B$4:$B$204,B123)=1)</formula1>
+      <formula1>AND(B123&lt;&gt;"",COUNTIF($B$4:$B$168,B123)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B124">
-      <formula1>AND(B124&lt;&gt;"",COUNTIF($B$4:$B$204,B124)=1)</formula1>
+      <formula1>AND(B124&lt;&gt;"",COUNTIF($B$4:$B$168,B124)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B125">
-      <formula1>AND(B125&lt;&gt;"",COUNTIF($B$4:$B$204,B125)=1)</formula1>
+      <formula1>AND(B125&lt;&gt;"",COUNTIF($B$4:$B$168,B125)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B126">
-      <formula1>AND(B126&lt;&gt;"",COUNTIF($B$4:$B$204,B126)=1)</formula1>
+      <formula1>AND(B126&lt;&gt;"",COUNTIF($B$4:$B$168,B126)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B127">
-      <formula1>AND(B127&lt;&gt;"",COUNTIF($B$4:$B$204,B127)=1)</formula1>
+      <formula1>AND(B127&lt;&gt;"",COUNTIF($B$4:$B$168,B127)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B128">
-      <formula1>AND(B128&lt;&gt;"",COUNTIF($B$4:$B$204,B128)=1)</formula1>
+      <formula1>AND(B128&lt;&gt;"",COUNTIF($B$4:$B$168,B128)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B129">
-      <formula1>AND(B129&lt;&gt;"",COUNTIF($B$4:$B$204,B129)=1)</formula1>
+      <formula1>AND(B129&lt;&gt;"",COUNTIF($B$4:$B$168,B129)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B130">
-      <formula1>AND(B130&lt;&gt;"",COUNTIF($B$4:$B$204,B130)=1)</formula1>
+      <formula1>AND(B130&lt;&gt;"",COUNTIF($B$4:$B$168,B130)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B131">
-      <formula1>AND(B131&lt;&gt;"",COUNTIF($B$4:$B$204,B131)=1)</formula1>
+      <formula1>AND(B131&lt;&gt;"",COUNTIF($B$4:$B$168,B131)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B132">
-      <formula1>AND(B132&lt;&gt;"",COUNTIF($B$4:$B$204,B132)=1)</formula1>
+      <formula1>AND(B132&lt;&gt;"",COUNTIF($B$4:$B$168,B132)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B133">
-      <formula1>AND(B133&lt;&gt;"",COUNTIF($B$4:$B$204,B133)=1)</formula1>
+      <formula1>AND(B133&lt;&gt;"",COUNTIF($B$4:$B$168,B133)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B134">
-      <formula1>AND(B134&lt;&gt;"",COUNTIF($B$4:$B$204,B134)=1)</formula1>
+      <formula1>AND(B134&lt;&gt;"",COUNTIF($B$4:$B$168,B134)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B135">
-      <formula1>AND(B135&lt;&gt;"",COUNTIF($B$4:$B$204,B135)=1)</formula1>
+      <formula1>AND(B135&lt;&gt;"",COUNTIF($B$4:$B$168,B135)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B136">
-      <formula1>AND(B136&lt;&gt;"",COUNTIF($B$4:$B$204,B136)=1)</formula1>
+      <formula1>AND(B136&lt;&gt;"",COUNTIF($B$4:$B$168,B136)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B137">
-      <formula1>AND(B137&lt;&gt;"",COUNTIF($B$4:$B$204,B137)=1)</formula1>
+      <formula1>AND(B137&lt;&gt;"",COUNTIF($B$4:$B$168,B137)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B138">
-      <formula1>AND(B138&lt;&gt;"",COUNTIF($B$4:$B$204,B138)=1)</formula1>
+      <formula1>AND(B138&lt;&gt;"",COUNTIF($B$4:$B$168,B138)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B139">
-      <formula1>AND(B139&lt;&gt;"",COUNTIF($B$4:$B$204,B139)=1)</formula1>
+      <formula1>AND(B139&lt;&gt;"",COUNTIF($B$4:$B$168,B139)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B140">
-      <formula1>AND(B140&lt;&gt;"",COUNTIF($B$4:$B$204,B140)=1)</formula1>
+      <formula1>AND(B140&lt;&gt;"",COUNTIF($B$4:$B$168,B140)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B141">
-      <formula1>AND(B141&lt;&gt;"",COUNTIF($B$4:$B$204,B141)=1)</formula1>
+      <formula1>AND(B141&lt;&gt;"",COUNTIF($B$4:$B$168,B141)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B142">
-      <formula1>AND(B142&lt;&gt;"",COUNTIF($B$4:$B$204,B142)=1)</formula1>
+      <formula1>AND(B142&lt;&gt;"",COUNTIF($B$4:$B$168,B142)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B143">
-      <formula1>AND(B143&lt;&gt;"",COUNTIF($B$4:$B$204,B143)=1)</formula1>
+      <formula1>AND(B143&lt;&gt;"",COUNTIF($B$4:$B$168,B143)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B144">
-      <formula1>AND(B144&lt;&gt;"",COUNTIF($B$4:$B$204,B144)=1)</formula1>
+      <formula1>AND(B144&lt;&gt;"",COUNTIF($B$4:$B$168,B144)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B145">
-      <formula1>AND(B145&lt;&gt;"",COUNTIF($B$4:$B$204,B145)=1)</formula1>
+      <formula1>AND(B145&lt;&gt;"",COUNTIF($B$4:$B$168,B145)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B146">
-      <formula1>AND(B146&lt;&gt;"",COUNTIF($B$4:$B$204,B146)=1)</formula1>
+      <formula1>AND(B146&lt;&gt;"",COUNTIF($B$4:$B$168,B146)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B147">
-      <formula1>AND(B147&lt;&gt;"",COUNTIF($B$4:$B$204,B147)=1)</formula1>
+      <formula1>AND(B147&lt;&gt;"",COUNTIF($B$4:$B$168,B147)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B148">
-      <formula1>AND(B148&lt;&gt;"",COUNTIF($B$4:$B$204,B148)=1)</formula1>
+      <formula1>AND(B148&lt;&gt;"",COUNTIF($B$4:$B$168,B148)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B149">
-      <formula1>AND(B149&lt;&gt;"",COUNTIF($B$4:$B$204,B149)=1)</formula1>
+      <formula1>AND(B149&lt;&gt;"",COUNTIF($B$4:$B$168,B149)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B150">
-      <formula1>AND(B150&lt;&gt;"",COUNTIF($B$4:$B$204,B150)=1)</formula1>
+      <formula1>AND(B150&lt;&gt;"",COUNTIF($B$4:$B$168,B150)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B151">
-      <formula1>AND(B151&lt;&gt;"",COUNTIF($B$4:$B$204,B151)=1)</formula1>
+      <formula1>AND(B151&lt;&gt;"",COUNTIF($B$4:$B$168,B151)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B152">
-      <formula1>AND(B152&lt;&gt;"",COUNTIF($B$4:$B$204,B152)=1)</formula1>
+      <formula1>AND(B152&lt;&gt;"",COUNTIF($B$4:$B$168,B152)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B153">
-      <formula1>AND(B153&lt;&gt;"",COUNTIF($B$4:$B$204,B153)=1)</formula1>
+      <formula1>AND(B153&lt;&gt;"",COUNTIF($B$4:$B$168,B153)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B154">
-      <formula1>AND(B154&lt;&gt;"",COUNTIF($B$4:$B$204,B154)=1)</formula1>
+      <formula1>AND(B154&lt;&gt;"",COUNTIF($B$4:$B$168,B154)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B155">
-      <formula1>AND(B155&lt;&gt;"",COUNTIF($B$4:$B$204,B155)=1)</formula1>
+      <formula1>AND(B155&lt;&gt;"",COUNTIF($B$4:$B$168,B155)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B156">
-      <formula1>AND(B156&lt;&gt;"",COUNTIF($B$4:$B$204,B156)=1)</formula1>
+      <formula1>AND(B156&lt;&gt;"",COUNTIF($B$4:$B$168,B156)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B157">
-      <formula1>AND(B157&lt;&gt;"",COUNTIF($B$4:$B$204,B157)=1)</formula1>
+      <formula1>AND(B157&lt;&gt;"",COUNTIF($B$4:$B$168,B157)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B158">
-      <formula1>AND(B158&lt;&gt;"",COUNTIF($B$4:$B$204,B158)=1)</formula1>
+      <formula1>AND(B158&lt;&gt;"",COUNTIF($B$4:$B$168,B158)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B159">
-      <formula1>AND(B159&lt;&gt;"",COUNTIF($B$4:$B$204,B159)=1)</formula1>
+      <formula1>AND(B159&lt;&gt;"",COUNTIF($B$4:$B$168,B159)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B160">
-      <formula1>AND(B160&lt;&gt;"",COUNTIF($B$4:$B$204,B160)=1)</formula1>
+      <formula1>AND(B160&lt;&gt;"",COUNTIF($B$4:$B$168,B160)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B161">
-      <formula1>AND(B161&lt;&gt;"",COUNTIF($B$4:$B$204,B161)=1)</formula1>
+      <formula1>AND(B161&lt;&gt;"",COUNTIF($B$4:$B$168,B161)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B162">
-      <formula1>AND(B162&lt;&gt;"",COUNTIF($B$4:$B$204,B162)=1)</formula1>
+      <formula1>AND(B162&lt;&gt;"",COUNTIF($B$4:$B$168,B162)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B163">
-      <formula1>AND(B163&lt;&gt;"",COUNTIF($B$4:$B$204,B163)=1)</formula1>
+      <formula1>AND(B163&lt;&gt;"",COUNTIF($B$4:$B$168,B163)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B164">
-      <formula1>AND(B164&lt;&gt;"",COUNTIF($B$4:$B$204,B164)=1)</formula1>
+      <formula1>AND(B164&lt;&gt;"",COUNTIF($B$4:$B$168,B164)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B165">
-      <formula1>AND(B165&lt;&gt;"",COUNTIF($B$4:$B$204,B165)=1)</formula1>
+      <formula1>AND(B165&lt;&gt;"",COUNTIF($B$4:$B$168,B165)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B166">
-      <formula1>AND(B166&lt;&gt;"",COUNTIF($B$4:$B$204,B166)=1)</formula1>
+      <formula1>AND(B166&lt;&gt;"",COUNTIF($B$4:$B$168,B166)=1)</formula1>
     </dataValidation>
     <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B167">
-      <formula1>AND(B167&lt;&gt;"",COUNTIF($B$4:$B$204,B167)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B168">
-      <formula1>AND(B168&lt;&gt;"",COUNTIF($B$4:$B$204,B168)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B169">
-      <formula1>AND(B169&lt;&gt;"",COUNTIF($B$4:$B$204,B169)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B170">
-      <formula1>AND(B170&lt;&gt;"",COUNTIF($B$4:$B$204,B170)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B171">
-      <formula1>AND(B171&lt;&gt;"",COUNTIF($B$4:$B$204,B171)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B172">
-      <formula1>AND(B172&lt;&gt;"",COUNTIF($B$4:$B$204,B172)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B173">
-      <formula1>AND(B173&lt;&gt;"",COUNTIF($B$4:$B$204,B173)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B174">
-      <formula1>AND(B174&lt;&gt;"",COUNTIF($B$4:$B$204,B174)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B175">
-      <formula1>AND(B175&lt;&gt;"",COUNTIF($B$4:$B$204,B175)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B176">
-      <formula1>AND(B176&lt;&gt;"",COUNTIF($B$4:$B$204,B176)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B177">
-      <formula1>AND(B177&lt;&gt;"",COUNTIF($B$4:$B$204,B177)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B178">
-      <formula1>AND(B178&lt;&gt;"",COUNTIF($B$4:$B$204,B178)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B179">
-      <formula1>AND(B179&lt;&gt;"",COUNTIF($B$4:$B$204,B179)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B180">
-      <formula1>AND(B180&lt;&gt;"",COUNTIF($B$4:$B$204,B180)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B181">
-      <formula1>AND(B181&lt;&gt;"",COUNTIF($B$4:$B$204,B181)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B182">
-      <formula1>AND(B182&lt;&gt;"",COUNTIF($B$4:$B$204,B182)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B183">
-      <formula1>AND(B183&lt;&gt;"",COUNTIF($B$4:$B$204,B183)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B184">
-      <formula1>AND(B184&lt;&gt;"",COUNTIF($B$4:$B$204,B184)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B185">
-      <formula1>AND(B185&lt;&gt;"",COUNTIF($B$4:$B$204,B185)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B186">
-      <formula1>AND(B186&lt;&gt;"",COUNTIF($B$4:$B$204,B186)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B187">
-      <formula1>AND(B187&lt;&gt;"",COUNTIF($B$4:$B$204,B187)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B188">
-      <formula1>AND(B188&lt;&gt;"",COUNTIF($B$4:$B$204,B188)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B189">
-      <formula1>AND(B189&lt;&gt;"",COUNTIF($B$4:$B$204,B189)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B190">
-      <formula1>AND(B190&lt;&gt;"",COUNTIF($B$4:$B$204,B190)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B191">
-      <formula1>AND(B191&lt;&gt;"",COUNTIF($B$4:$B$204,B191)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B192">
-      <formula1>AND(B192&lt;&gt;"",COUNTIF($B$4:$B$204,B192)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B193">
-      <formula1>AND(B193&lt;&gt;"",COUNTIF($B$4:$B$204,B193)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B194">
-      <formula1>AND(B194&lt;&gt;"",COUNTIF($B$4:$B$204,B194)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B195">
-      <formula1>AND(B195&lt;&gt;"",COUNTIF($B$4:$B$204,B195)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B196">
-      <formula1>AND(B196&lt;&gt;"",COUNTIF($B$4:$B$204,B196)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B197">
-      <formula1>AND(B197&lt;&gt;"",COUNTIF($B$4:$B$204,B197)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B198">
-      <formula1>AND(B198&lt;&gt;"",COUNTIF($B$4:$B$204,B198)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B199">
-      <formula1>AND(B199&lt;&gt;"",COUNTIF($B$4:$B$204,B199)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B200">
-      <formula1>AND(B200&lt;&gt;"",COUNTIF($B$4:$B$204,B200)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B201">
-      <formula1>AND(B201&lt;&gt;"",COUNTIF($B$4:$B$204,B201)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B202">
-      <formula1>AND(B202&lt;&gt;"",COUNTIF($B$4:$B$204,B202)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID重复" error="每件物品使用不同的ID。" sqref="B203">
-      <formula1>AND(B203&lt;&gt;"",COUNTIF($B$4:$B$204,B203)=1)</formula1>
+      <formula1>AND(B167&lt;&gt;"",COUNTIF($B$4:$B$168,B167)=1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6067,7 +4826,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="B25"/>
+  <dimension ref="B19"/>
   <cols>
     <col min="1" max="1" width="14.7109" customWidth="1"/>
     <col min="2" max="3" width="10.793" customWidth="1"/>
@@ -6137,7 +4896,7 @@
         <v>323</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -6151,7 +4910,7 @@
         <v>325</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -6165,234 +4924,150 @@
         <v>327</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>332</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>334</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
         <v>335</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>337</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" t="s">
-        <v>197</v>
+        <v>351</v>
       </c>
       <c r="C11" t="s">
         <v>335</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>339</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="C12" t="s">
         <v>335</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>341</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" t="s">
-        <v>342</v>
+        <v>244</v>
       </c>
       <c r="C13" t="s">
         <v>335</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" t="s">
-        <v>335</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
-      <c r="B16" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" t="s">
-        <v>335</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>359</v>
+      </c>
       <c r="B17" t="s">
-        <v>351</v>
-      </c>
-      <c r="C17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>359</v>
+      </c>
       <c r="B18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C18" t="s">
-        <v>335</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>359</v>
+      </c>
       <c r="B19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C19" t="s">
-        <v>335</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" t="s">
-        <v>251</v>
-      </c>
-      <c r="C20" t="s">
-        <v>357</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>359</v>
-      </c>
-      <c r="B23" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>359</v>
-      </c>
-      <c r="B24" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>359</v>
-      </c>
-      <c r="B25" t="s">
         <v>363</v>
       </c>
     </row>
@@ -6532,7 +5207,10 @@
         <v>377</v>
       </c>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="2:4">
+      <c r="B10" s="4">
+        <v>6</v>
+      </c>
       <c r="D10" t="s">
         <v>378</v>
       </c>

--- a/Excel/Item.xlsx
+++ b/Excel/Item.xlsx
@@ -26,8 +26,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={CD602728-33A3-4002-BBFC-6F1BB7A6A301}</author>
-    <author>tc={66998419-ED7C-48BD-8F52-149E19777794}</author>
+    <author>tc={62A7FB6D-3B3A-4B9E-83F4-66709CEC2FCC}</author>
+    <author>tc={49B4E026-2C88-4690-8EAA-4806DC9B055E}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="415">
   <si>
     <t/>
   </si>
@@ -1230,6 +1230,78 @@
   </si>
   <si>
     <t>intelligence</t>
+  </si>
+  <si>
+    <t>icon_1.png</t>
+  </si>
+  <si>
+    <t>icon_2_.png</t>
+  </si>
+  <si>
+    <t>icon_3.png</t>
+  </si>
+  <si>
+    <t>icon_4_.png</t>
+  </si>
+  <si>
+    <t>icon_5.png</t>
+  </si>
+  <si>
+    <t>icon_6.png</t>
+  </si>
+  <si>
+    <t>icon_7.png</t>
+  </si>
+  <si>
+    <t>icon_8_.png</t>
+  </si>
+  <si>
+    <t>icon_9.png</t>
+  </si>
+  <si>
+    <t>icon_10.png</t>
+  </si>
+  <si>
+    <t>icon_11.png</t>
+  </si>
+  <si>
+    <t>icon_12.png</t>
+  </si>
+  <si>
+    <t>icon_13.png</t>
+  </si>
+  <si>
+    <t>icon_14.png</t>
+  </si>
+  <si>
+    <t>icon_15_.png</t>
+  </si>
+  <si>
+    <t>icon_16.png</t>
+  </si>
+  <si>
+    <t>icon_17.png</t>
+  </si>
+  <si>
+    <t>icon_18.png</t>
+  </si>
+  <si>
+    <t>icon_19.png</t>
+  </si>
+  <si>
+    <t>icon_20.png</t>
+  </si>
+  <si>
+    <t>icon_21.png</t>
+  </si>
+  <si>
+    <t>icon_22.png</t>
+  </si>
+  <si>
+    <t>icon_23.png</t>
+  </si>
+  <si>
+    <t>icon_24.png</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1378,7 @@
   <cellStyleXfs>
     <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1328,9 +1400,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1354,7 +1423,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <tc2018:personList xmlns:tc2018="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="tc2018">
-  <tc2018:person displayName="銀河騎士" id="{F60A727E-0A88-4B99-9DF1-06B02B75AFB4}"/>
+  <tc2018:person displayName="銀河騎士" id="{CA55F165-65EC-467B-A8FD-CAF3FC8F6F3E}"/>
 </tc2018:personList>
 </file>
 
@@ -1621,7 +1690,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="">
-  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{F60A727E-0A88-4B99-9DF1-06B02B75AFB4}" id="{CD602728-33A3-4002-BBFC-6F1BB7A6A301}">
+  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{CA55F165-65EC-467B-A8FD-CAF3FC8F6F3E}" id="{62A7FB6D-3B3A-4B9E-83F4-66709CEC2FCC}">
     <text>0=货币
 1=武器
 2=防具
@@ -1629,7 +1698,7 @@
 4=材料
 5=消耗品</text>
   </threadedComment>
-  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{F60A727E-0A88-4B99-9DF1-06B02B75AFB4}" id="{66998419-ED7C-48BD-8F52-149E19777794}">
+  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{CA55F165-65EC-467B-A8FD-CAF3FC8F6F3E}" id="{49B4E026-2C88-4690-8EAA-4806DC9B055E}">
     <text>1=普通
 2=稀有
 3=史诗
@@ -1828,7 +1897,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>37</v>
+        <v>391</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -1883,7 +1952,7 @@
         <v>42</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>392</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
@@ -1938,7 +2007,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>49</v>
+        <v>393</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
@@ -1990,7 +2059,7 @@
         <v>53</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>54</v>
+        <v>394</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -2036,7 +2105,7 @@
         <v>56</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>57</v>
+        <v>395</v>
       </c>
       <c r="E8" s="4">
         <v>1</v>
@@ -2082,7 +2151,7 @@
         <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -2128,7 +2197,7 @@
         <v>62</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>63</v>
+        <v>397</v>
       </c>
       <c r="E10" s="4">
         <v>3</v>
@@ -2174,7 +2243,7 @@
         <v>65</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>66</v>
+        <v>398</v>
       </c>
       <c r="E11" s="4">
         <v>4</v>
@@ -2220,7 +2289,7 @@
         <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>69</v>
+        <v>399</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
@@ -2266,7 +2335,7 @@
         <v>71</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>72</v>
+        <v>400</v>
       </c>
       <c r="E13" s="4">
         <v>3</v>
@@ -2312,7 +2381,7 @@
         <v>74</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>75</v>
+        <v>401</v>
       </c>
       <c r="E14" s="4">
         <v>4</v>
@@ -2358,7 +2427,7 @@
         <v>77</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
@@ -2404,7 +2473,7 @@
         <v>80</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="E16" s="4">
         <v>3</v>
@@ -2450,7 +2519,7 @@
         <v>83</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="E17" s="4">
         <v>4</v>
@@ -2496,7 +2565,7 @@
         <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>87</v>
+        <v>405</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -2542,7 +2611,7 @@
         <v>89</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>406</v>
       </c>
       <c r="E19" s="4">
         <v>3</v>
@@ -2588,7 +2657,7 @@
         <v>92</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>93</v>
+        <v>407</v>
       </c>
       <c r="E20" s="4">
         <v>4</v>
@@ -2634,7 +2703,7 @@
         <v>95</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>96</v>
+        <v>408</v>
       </c>
       <c r="E21" s="4">
         <v>1</v>
@@ -2680,7 +2749,7 @@
         <v>98</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>99</v>
+        <v>409</v>
       </c>
       <c r="E22" s="4">
         <v>3</v>
@@ -2726,7 +2795,7 @@
         <v>101</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>102</v>
+        <v>410</v>
       </c>
       <c r="E23" s="4">
         <v>4</v>
@@ -2772,7 +2841,7 @@
         <v>104</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="E24" s="4">
         <v>3</v>
@@ -2818,7 +2887,7 @@
         <v>107</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>108</v>
+        <v>412</v>
       </c>
       <c r="E25" s="4">
         <v>4</v>
@@ -2864,7 +2933,7 @@
         <v>110</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>111</v>
+        <v>413</v>
       </c>
       <c r="E26" s="4">
         <v>3</v>
@@ -2910,7 +2979,7 @@
         <v>113</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>114</v>
+        <v>414</v>
       </c>
       <c r="E27" s="4">
         <v>4</v>
@@ -4123,43 +4192,43 @@
       <c r="B54" s="8">
         <v>51</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="14">
         <v>1</v>
       </c>
-      <c r="F54" s="15">
+      <c r="F54" s="14">
         <v>6</v>
       </c>
-      <c r="G54" s="15" t="s">
+      <c r="G54" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="H54" s="15">
+      <c r="H54" s="14">
         <v>45</v>
       </c>
-      <c r="I54" s="15">
-        <v>0</v>
-      </c>
-      <c r="J54" s="15">
-        <v>0</v>
-      </c>
-      <c r="K54" s="15">
-        <v>0</v>
-      </c>
-      <c r="L54" s="15">
-        <v>0</v>
-      </c>
-      <c r="M54" s="15">
-        <v>0</v>
-      </c>
-      <c r="N54" s="15">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="s">
+      <c r="I54" s="14">
+        <v>0</v>
+      </c>
+      <c r="J54" s="14">
+        <v>0</v>
+      </c>
+      <c r="K54" s="14">
+        <v>0</v>
+      </c>
+      <c r="L54" s="14">
+        <v>0</v>
+      </c>
+      <c r="M54" s="14">
+        <v>0</v>
+      </c>
+      <c r="N54" s="14">
+        <v>0</v>
+      </c>
+      <c r="O54" s="14" t="s">
         <v>256</v>
       </c>
     </row>
@@ -4211,43 +4280,43 @@
       <c r="B56" s="8">
         <v>53</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="E56" s="15">
+      <c r="E56" s="14">
         <v>2</v>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="14">
         <v>6</v>
       </c>
-      <c r="G56" s="15" t="s">
+      <c r="G56" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="H56" s="15">
+      <c r="H56" s="14">
         <v>100</v>
       </c>
-      <c r="I56" s="15">
-        <v>0</v>
-      </c>
-      <c r="J56" s="15">
-        <v>0</v>
-      </c>
-      <c r="K56" s="15">
-        <v>0</v>
-      </c>
-      <c r="L56" s="15">
-        <v>0</v>
-      </c>
-      <c r="M56" s="15">
-        <v>0</v>
-      </c>
-      <c r="N56" s="15">
-        <v>0</v>
-      </c>
-      <c r="O56" s="15" t="s">
+      <c r="I56" s="14">
+        <v>0</v>
+      </c>
+      <c r="J56" s="14">
+        <v>0</v>
+      </c>
+      <c r="K56" s="14">
+        <v>0</v>
+      </c>
+      <c r="L56" s="14">
+        <v>0</v>
+      </c>
+      <c r="M56" s="14">
+        <v>0</v>
+      </c>
+      <c r="N56" s="14">
+        <v>0</v>
+      </c>
+      <c r="O56" s="14" t="s">
         <v>268</v>
       </c>
     </row>
@@ -4255,43 +4324,43 @@
       <c r="B57" s="8">
         <v>54</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="E57" s="15">
+      <c r="E57" s="14">
         <v>3</v>
       </c>
-      <c r="F57" s="15">
+      <c r="F57" s="14">
         <v>6</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="H57" s="15">
+      <c r="H57" s="14">
         <v>150</v>
       </c>
-      <c r="I57" s="15">
-        <v>0</v>
-      </c>
-      <c r="J57" s="15">
-        <v>0</v>
-      </c>
-      <c r="K57" s="15">
-        <v>0</v>
-      </c>
-      <c r="L57" s="15">
-        <v>0</v>
-      </c>
-      <c r="M57" s="15">
-        <v>0</v>
-      </c>
-      <c r="N57" s="15">
-        <v>0</v>
-      </c>
-      <c r="O57" s="15" t="s">
+      <c r="I57" s="14">
+        <v>0</v>
+      </c>
+      <c r="J57" s="14">
+        <v>0</v>
+      </c>
+      <c r="K57" s="14">
+        <v>0</v>
+      </c>
+      <c r="L57" s="14">
+        <v>0</v>
+      </c>
+      <c r="M57" s="14">
+        <v>0</v>
+      </c>
+      <c r="N57" s="14">
+        <v>0</v>
+      </c>
+      <c r="O57" s="14" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4835,53 +4904,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="5" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4892,10 +4961,10 @@
       <c r="C4" t="s">
         <v>322</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>383</v>
       </c>
     </row>
@@ -4906,10 +4975,10 @@
       <c r="C5" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>384</v>
       </c>
     </row>
@@ -4920,10 +4989,10 @@
       <c r="C6" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>385</v>
       </c>
     </row>
@@ -4934,10 +5003,10 @@
       <c r="C7" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>337</v>
       </c>
     </row>
@@ -4948,10 +5017,10 @@
       <c r="C8" t="s">
         <v>335</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4962,10 +5031,10 @@
       <c r="C9" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>387</v>
       </c>
     </row>
@@ -4976,10 +5045,10 @@
       <c r="C10" t="s">
         <v>335</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>238</v>
       </c>
     </row>
@@ -4990,10 +5059,10 @@
       <c r="C11" t="s">
         <v>335</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5004,10 +5073,10 @@
       <c r="C12" t="s">
         <v>335</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>388</v>
       </c>
     </row>
@@ -5018,10 +5087,10 @@
       <c r="C13" t="s">
         <v>335</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5032,18 +5101,18 @@
       <c r="C14" t="s">
         <v>357</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>360</v>
       </c>
     </row>
@@ -5110,10 +5179,10 @@
       <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E2" t="s">
@@ -5121,10 +5190,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -5133,7 +5202,7 @@
       <c r="D3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5141,8 +5210,8 @@
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="14" t="s"/>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="13" t="s"/>
+      <c r="D4" s="13" t="s">
         <v>365</v>
       </c>
       <c r="E4" t="s">

--- a/Excel/Item.xlsx
+++ b/Excel/Item.xlsx
@@ -26,8 +26,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={62A7FB6D-3B3A-4B9E-83F4-66709CEC2FCC}</author>
-    <author>tc={49B4E026-2C88-4690-8EAA-4806DC9B055E}</author>
+    <author>tc={5110000D-0D91-4FF6-BE65-013BCBC0B948}</author>
+    <author>tc={21B16FA7-180E-49CA-BBBA-5215789ADF4F}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
   <si>
     <t/>
   </si>
@@ -1302,6 +1302,12 @@
   </si>
   <si>
     <t>icon_24.png</t>
+  </si>
+  <si>
+    <t>情报</t>
+  </si>
+  <si>
+    <t>情报信息</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +1429,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <tc2018:personList xmlns:tc2018="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="tc2018">
-  <tc2018:person displayName="銀河騎士" id="{CA55F165-65EC-467B-A8FD-CAF3FC8F6F3E}"/>
+  <tc2018:person displayName="銀河騎士" id="{73E7B617-4E64-4B94-A2BB-B0B69DFF0DE0}"/>
 </tc2018:personList>
 </file>
 
@@ -1690,7 +1696,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="">
-  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{CA55F165-65EC-467B-A8FD-CAF3FC8F6F3E}" id="{62A7FB6D-3B3A-4B9E-83F4-66709CEC2FCC}">
+  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{73E7B617-4E64-4B94-A2BB-B0B69DFF0DE0}" id="{5110000D-0D91-4FF6-BE65-013BCBC0B948}">
     <text>0=货币
 1=武器
 2=防具
@@ -1698,7 +1704,7 @@
 4=材料
 5=消耗品</text>
   </threadedComment>
-  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{CA55F165-65EC-467B-A8FD-CAF3FC8F6F3E}" id="{49B4E026-2C88-4690-8EAA-4806DC9B055E}">
+  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{73E7B617-4E64-4B94-A2BB-B0B69DFF0DE0}" id="{21B16FA7-180E-49CA-BBBA-5215789ADF4F}">
     <text>1=普通
 2=稀有
 3=史诗
@@ -4452,7 +4458,47 @@
         <v>288</v>
       </c>
     </row>
-    <row r="60" spans="1:30" ht="24" customHeight="1"/>
+    <row r="60" spans="2:15" ht="24" customHeight="1">
+      <c r="B60">
+        <v>57</v>
+      </c>
+      <c r="C60" t="s">
+        <v>415</v>
+      </c>
+      <c r="D60" t="s">
+        <v>290</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="H60">
+        <v>50</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>416</v>
+      </c>
+    </row>
     <row r="61" spans="1:30" ht="24" customHeight="1"/>
     <row r="62" spans="1:30" ht="24" customHeight="1"/>
     <row r="63" spans="1:30" ht="24" customHeight="1"/>

--- a/Excel/Item.xlsx
+++ b/Excel/Item.xlsx
@@ -26,8 +26,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={5110000D-0D91-4FF6-BE65-013BCBC0B948}</author>
-    <author>tc={21B16FA7-180E-49CA-BBBA-5215789ADF4F}</author>
+    <author>tc={A4D2E04E-E0FE-45A0-85B0-F5C725D71BAC}</author>
+    <author>tc={A3D9FF75-D462-44FC-807F-9C81A66FEB5C}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0">
@@ -1429,7 +1429,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <tc2018:personList xmlns:tc2018="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="tc2018">
-  <tc2018:person displayName="銀河騎士" id="{73E7B617-4E64-4B94-A2BB-B0B69DFF0DE0}"/>
+  <tc2018:person displayName="銀河騎士" id="{8A8E360B-E082-4F28-86D2-6AC3B93E4945}"/>
 </tc2018:personList>
 </file>
 
@@ -1696,7 +1696,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="">
-  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{73E7B617-4E64-4B94-A2BB-B0B69DFF0DE0}" id="{5110000D-0D91-4FF6-BE65-013BCBC0B948}">
+  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{8A8E360B-E082-4F28-86D2-6AC3B93E4945}" id="{A4D2E04E-E0FE-45A0-85B0-F5C725D71BAC}">
     <text>0=货币
 1=武器
 2=防具
@@ -1704,7 +1704,7 @@
 4=材料
 5=消耗品</text>
   </threadedComment>
-  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{73E7B617-4E64-4B94-A2BB-B0B69DFF0DE0}" id="{21B16FA7-180E-49CA-BBBA-5215789ADF4F}">
+  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{8A8E360B-E082-4F28-86D2-6AC3B93E4945}" id="{A3D9FF75-D462-44FC-807F-9C81A66FEB5C}">
     <text>1=普通
 2=稀有
 3=史诗

--- a/Excel/Item.xlsx
+++ b/Excel/Item.xlsx
@@ -26,8 +26,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={A4D2E04E-E0FE-45A0-85B0-F5C725D71BAC}</author>
-    <author>tc={A3D9FF75-D462-44FC-807F-9C81A66FEB5C}</author>
+    <author>tc={15772489-7306-4618-BD71-AFDDB07FE8BC}</author>
+    <author>tc={D3FE1206-323D-44C8-8F66-E53579FA3A4A}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0">
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
   <si>
     <t/>
   </si>
@@ -1308,6 +1308,57 @@
   </si>
   <si>
     <t>情报信息</t>
+  </si>
+  <si>
+    <t>icon_41_.png</t>
+  </si>
+  <si>
+    <t>icon_42_.png</t>
+  </si>
+  <si>
+    <t>icon_43_.png</t>
+  </si>
+  <si>
+    <t>icon_47_.png</t>
+  </si>
+  <si>
+    <t>icon_50_.png</t>
+  </si>
+  <si>
+    <t>icon_54.png</t>
+  </si>
+  <si>
+    <t>icon_55_.png</t>
+  </si>
+  <si>
+    <t>icon_56_.png</t>
+  </si>
+  <si>
+    <t>icon_60_.png</t>
+  </si>
+  <si>
+    <t>icon_62_.png</t>
+  </si>
+  <si>
+    <t>icon_64_.png</t>
+  </si>
+  <si>
+    <t>icon_66_.png</t>
+  </si>
+  <si>
+    <t>icon_68_.png</t>
+  </si>
+  <si>
+    <t>icon_69_.png</t>
+  </si>
+  <si>
+    <t>icon_71_.png</t>
+  </si>
+  <si>
+    <t>icon_72_.png</t>
+  </si>
+  <si>
+    <t>icon_74.png</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1435,7 @@
   <cellStyleXfs>
     <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1420,6 +1471,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1429,7 +1488,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <tc2018:personList xmlns:tc2018="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="tc2018">
-  <tc2018:person displayName="銀河騎士" id="{8A8E360B-E082-4F28-86D2-6AC3B93E4945}"/>
+  <tc2018:person displayName="銀河騎士" id="{B87B65E4-010D-4885-8B9A-E3C7F7AAB2FA}"/>
 </tc2018:personList>
 </file>
 
@@ -1696,7 +1755,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="">
-  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{8A8E360B-E082-4F28-86D2-6AC3B93E4945}" id="{A4D2E04E-E0FE-45A0-85B0-F5C725D71BAC}">
+  <threadedComment ref="F1" dT="2026-10-07T09:13:12Z" personId="{B87B65E4-010D-4885-8B9A-E3C7F7AAB2FA}" id="{15772489-7306-4618-BD71-AFDDB07FE8BC}">
     <text>0=货币
 1=武器
 2=防具
@@ -1704,7 +1763,7 @@
 4=材料
 5=消耗品</text>
   </threadedComment>
-  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{8A8E360B-E082-4F28-86D2-6AC3B93E4945}" id="{A3D9FF75-D462-44FC-807F-9C81A66FEB5C}">
+  <threadedComment ref="E1" dT="2026-10-07T09:15:09Z" personId="{B87B65E4-010D-4885-8B9A-E3C7F7AAB2FA}" id="{D3FE1206-323D-44C8-8F66-E53579FA3A4A}">
     <text>1=普通
 2=稀有
 3=史诗
@@ -1722,7 +1781,7 @@
     <col min="1" max="1" width="14.7109" customWidth="1"/>
     <col min="2" max="2" width="3.0625" customWidth="1"/>
     <col min="3" max="3" width="11.043" customWidth="1"/>
-    <col min="4" max="4" width="10.3008" customWidth="1"/>
+    <col min="4" max="4" width="16.1914" customWidth="1"/>
     <col min="5" max="5" width="6.30078" customWidth="1"/>
     <col min="6" max="6" width="9.07031" customWidth="1"/>
     <col min="7" max="7" width="28.4531" customWidth="1"/>
@@ -3673,8 +3732,8 @@
       <c r="C42" t="s">
         <v>166</v>
       </c>
-      <c r="D42" t="s">
-        <v>167</v>
+      <c r="D42" s="17" t="s">
+        <v>417</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3717,8 +3776,8 @@
       <c r="C43" t="s">
         <v>169</v>
       </c>
-      <c r="D43" t="s">
-        <v>170</v>
+      <c r="D43" s="17" t="s">
+        <v>418</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -3761,8 +3820,8 @@
       <c r="C44" t="s">
         <v>172</v>
       </c>
-      <c r="D44" t="s">
-        <v>173</v>
+      <c r="D44" s="17" t="s">
+        <v>419</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -3805,8 +3864,8 @@
       <c r="C45" t="s">
         <v>184</v>
       </c>
-      <c r="D45" t="s">
-        <v>185</v>
+      <c r="D45" s="17" t="s">
+        <v>420</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -3849,8 +3908,8 @@
       <c r="C46" t="s">
         <v>195</v>
       </c>
-      <c r="D46" t="s">
-        <v>196</v>
+      <c r="D46" s="17" t="s">
+        <v>421</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -3893,8 +3952,8 @@
       <c r="C47" t="s">
         <v>210</v>
       </c>
-      <c r="D47" t="s">
-        <v>211</v>
+      <c r="D47" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3937,8 +3996,8 @@
       <c r="C48" t="s">
         <v>213</v>
       </c>
-      <c r="D48" t="s">
-        <v>214</v>
+      <c r="D48" s="17" t="s">
+        <v>423</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3981,8 +4040,8 @@
       <c r="C49" t="s">
         <v>216</v>
       </c>
-      <c r="D49" t="s">
-        <v>217</v>
+      <c r="D49" s="17" t="s">
+        <v>424</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -4025,8 +4084,8 @@
       <c r="C50" t="s">
         <v>230</v>
       </c>
-      <c r="D50" t="s">
-        <v>231</v>
+      <c r="D50" s="17" t="s">
+        <v>425</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -4069,8 +4128,8 @@
       <c r="C51" t="s">
         <v>238</v>
       </c>
-      <c r="D51" t="s">
-        <v>239</v>
+      <c r="D51" s="17" t="s">
+        <v>426</v>
       </c>
       <c r="E51">
         <v>2</v>
@@ -4113,8 +4172,8 @@
       <c r="C52" t="s">
         <v>246</v>
       </c>
-      <c r="D52" t="s">
-        <v>247</v>
+      <c r="D52" s="17" t="s">
+        <v>427</v>
       </c>
       <c r="E52">
         <v>2</v>
@@ -4201,8 +4260,8 @@
       <c r="C54" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D54" s="14" t="s">
-        <v>254</v>
+      <c r="D54" s="15" t="s">
+        <v>428</v>
       </c>
       <c r="E54" s="14">
         <v>1</v>
@@ -4245,8 +4304,8 @@
       <c r="C55" t="s">
         <v>261</v>
       </c>
-      <c r="D55" t="s">
-        <v>262</v>
+      <c r="D55" s="18" t="s">
+        <v>429</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -4289,8 +4348,8 @@
       <c r="C56" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D56" s="14" t="s">
-        <v>266</v>
+      <c r="D56" s="15" t="s">
+        <v>430</v>
       </c>
       <c r="E56" s="14">
         <v>2</v>
@@ -4333,8 +4392,8 @@
       <c r="C57" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>274</v>
+      <c r="D57" s="15" t="s">
+        <v>431</v>
       </c>
       <c r="E57" s="14">
         <v>3</v>
@@ -4377,8 +4436,8 @@
       <c r="C58" t="s">
         <v>277</v>
       </c>
-      <c r="D58" t="s">
-        <v>278</v>
+      <c r="D58" s="18" t="s">
+        <v>432</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -4421,8 +4480,8 @@
       <c r="C59" t="s">
         <v>285</v>
       </c>
-      <c r="D59" t="s">
-        <v>286</v>
+      <c r="D59" s="18" t="s">
+        <v>433</v>
       </c>
       <c r="E59">
         <v>1</v>
